--- a/virtual-physics-lab/app/dl/DHS_Q2_resistor_network.xlsx
+++ b/virtual-physics-lab/app/dl/DHS_Q2_resistor_network.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +100,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -674,51 +675,51 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>11.65</v>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>13.3</v>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>17.32</v>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>26.17</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>55.63</v>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -798,14 +799,14 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>11.65</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>A6^2/(A6+1)</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>1000/B6</f>
         <v/>
       </c>
@@ -814,7 +815,7 @@
           <t>gradient = −R/E</t>
         </is>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>SLOPE(D6:D10,C6:C10)</f>
         <v/>
       </c>
@@ -828,14 +829,14 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>13.3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>A7^2/(A7+1)</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>1000/B7</f>
         <v/>
       </c>
@@ -844,7 +845,7 @@
           <t>y-intercept = 4R/E</t>
         </is>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <f>INTERCEPT(D6:D10,C6:C10)</f>
         <v/>
       </c>
@@ -858,14 +859,14 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>17.32</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>A8^2/(A8+1)</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>1000/B8</f>
         <v/>
       </c>
@@ -874,7 +875,7 @@
           <t>x-intercept</t>
         </is>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f>-INTERCEPT(D6:D10,C6:C10)/SLOPE(D6:D10,C6:C10)</f>
         <v/>
       </c>
@@ -884,14 +885,14 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>26.17</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>A9^2/(A9+1)</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>1000/B9</f>
         <v/>
       </c>
@@ -900,7 +901,7 @@
           <t>R = −gradient × E (E = 1.55 V)</t>
         </is>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f>-SLOPE(D6:D10,C6:C10)*1.55</f>
         <v/>
       </c>
@@ -914,14 +915,14 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>55.63</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>A10^2/(A10+1)</f>
         <v/>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>1000/B10</f>
         <v/>
       </c>
